--- a/Дело3а-78-2026Таганай/01_Иск/01.8_НПА_методические_материалы/В Правительство и в суд/Ходатайство об устранении недостатков и документы/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.8_НПА_методические_материалы/В Правительство и в суд/Ходатайство об устранении недостатков и документы/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92561350735</v>
+        <v>46157.9306713763</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.8_НПА_методические_материалы/В Правительство и в суд/Ходатайство об устранении недостатков и документы/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.8_НПА_методические_материалы/В Правительство и в суд/Ходатайство об устранении недостатков и документы/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.9306713763</v>
+        <v>46157.93151182508</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.8_НПА_методические_материалы/В Правительство и в суд/Ходатайство об устранении недостатков и документы/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.8_НПА_методические_материалы/В Правительство и в суд/Ходатайство об устранении недостатков и документы/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93151182508</v>
+        <v>46157.93393017833</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.8_НПА_методические_материалы/В Правительство и в суд/Ходатайство об устранении недостатков и документы/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.8_НПА_методические_материалы/В Правительство и в суд/Ходатайство об устранении недостатков и документы/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93393017833</v>
+        <v>46157.93706841259</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.8_НПА_методические_материалы/В Правительство и в суд/Ходатайство об устранении недостатков и документы/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.8_НПА_методические_материалы/В Правительство и в суд/Ходатайство об устранении недостатков и документы/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93706841259</v>
+        <v>46158.28210098559</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.8_НПА_методические_материалы/В Правительство и в суд/Ходатайство об устранении недостатков и документы/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.8_НПА_методические_материалы/В Правительство и в суд/Ходатайство об устранении недостатков и документы/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28210098559</v>
+        <v>46158.29664936305</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.8_НПА_методические_материалы/В Правительство и в суд/Ходатайство об устранении недостатков и документы/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.8_НПА_методические_материалы/В Правительство и в суд/Ходатайство об устранении недостатков и документы/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29664936305</v>
+        <v>46158.29803819579</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.8_НПА_методические_материалы/В Правительство и в суд/Ходатайство об устранении недостатков и документы/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.8_НПА_методические_материалы/В Правительство и в суд/Ходатайство об устранении недостатков и документы/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29803819579</v>
+        <v>46158.33380785394</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.8_НПА_методические_материалы/В Правительство и в суд/Ходатайство об устранении недостатков и документы/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.8_НПА_методические_материалы/В Правительство и в суд/Ходатайство об устранении недостатков и документы/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33380785394</v>
+        <v>46158.36847013913</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.8_НПА_методические_материалы/В Правительство и в суд/Ходатайство об устранении недостатков и документы/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.8_НПА_методические_материалы/В Правительство и в суд/Ходатайство об устранении недостатков и документы/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36847013913</v>
+        <v>46158.37281035447</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
